--- a/Result/profitability/4417.xlsx
+++ b/Result/profitability/4417.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>1.23125</v>
+        <v>1.26125</v>
       </c>
       <c r="N2" t="n">
-        <v>28.25875</v>
+        <v>28.905</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.31</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1125</v>
+        <v>1.12125</v>
       </c>
       <c r="N3" t="n">
-        <v>26.4775</v>
+        <v>26.96</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0.98625</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>24.9975</v>
+        <v>25.48875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73375</v>
       </c>
       <c r="N5" t="n">
-        <v>23.3075</v>
+        <v>23.86375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.34</v>
       </c>
       <c r="M6" t="n">
-        <v>0.58875</v>
+        <v>0.5975</v>
       </c>
       <c r="N6" t="n">
-        <v>21.7525</v>
+        <v>21.72125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.42</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4625</v>
+        <v>0.47</v>
       </c>
       <c r="N7" t="n">
-        <v>20.07625</v>
+        <v>20.58125</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.21</v>
       </c>
       <c r="M8" t="n">
-        <v>0.30875</v>
+        <v>0.3925</v>
       </c>
       <c r="N8" t="n">
-        <v>18.545</v>
+        <v>18.95875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4417</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>871</v>
+      </c>
+      <c r="D75" t="n">
+        <v>577</v>
+      </c>
+      <c r="E75" t="n">
+        <v>294</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>206</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>23.65%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>190</v>
+      </c>
+      <c r="K75" t="n">
+        <v>126</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.39375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.70625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8072289156626506</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.310000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1086671043992122</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.6099999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2890995260663507</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.450000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1517735334242838</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
